--- a/VerveStacks_CHN_grids_kan10/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_CHN_grids_kan10/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B8110613-B35D-4600-BA73-9B6AB34533F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{60E735AA-F773-4AC2-B802-63D35509A95D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="21600" windowHeight="12683" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grids" sheetId="6" r:id="rId1"/>
@@ -1829,7 +1829,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A13DF910-CE5C-4C0B-BC08-19A8212C049B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07ECE403-4268-4C89-A3DB-17C56FD4393F}">
   <dimension ref="B2:AF201"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5518,7 +5518,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4253C777-D7FE-4C72-BE2A-4DE6B62C2A7B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{210DD58F-231E-4094-8BE0-CA2D0821C974}">
   <dimension ref="B9:L24"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_CHN_grids_kan10/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_CHN_grids_kan10/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHN_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{60E735AA-F773-4AC2-B802-63D35509A95D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F7CE350D-8A74-47FD-A7EF-7A53948A195E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1829,7 +1829,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07ECE403-4268-4C89-A3DB-17C56FD4393F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41C735C4-7A53-454E-B63F-01229992E35D}">
   <dimension ref="B2:AF201"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5518,7 +5518,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{210DD58F-231E-4094-8BE0-CA2D0821C974}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AD7C742-90F9-42DC-81A4-3011F102B307}">
   <dimension ref="B9:L24"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
